--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/SpecializationForm.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/SpecializationForm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED7F27B7-6B1A-4220-A8DA-806BB784B057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03D6739-C4D3-4F66-BE70-9D7B0E44681E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5910" windowWidth="44100" windowHeight="14560" xr2:uid="{0D895801-8066-4166-8D52-EDF37837404A}"/>
+    <workbookView xWindow="0" yWindow="5910" windowWidth="44100" windowHeight="14560" xr2:uid="{38AF9ABE-2DCC-4D96-A8AB-30D7CE7A8C0A}"/>
   </bookViews>
   <sheets>
     <sheet name="SpecializationForm" sheetId="2" r:id="rId1"/>
@@ -71,46 +71,46 @@
     <t>解锁等级</t>
   </si>
   <si>
-    <t>NameKey</t>
+    <t>Name</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
-    <t>形态名多语言Key(仅客户端)</t>
+    <t>形态名-中文原文(仅客户端)</t>
   </si>
   <si>
     <t>ArtKey</t>
   </si>
   <si>
-    <t>立绘Addressable Key(仅客户端)</t>
+    <t>立绘Addressable完整路径(仅客户端)</t>
   </si>
   <si>
     <t>IconKey</t>
   </si>
   <si>
-    <t>头像Addressable Key(仅客户端)</t>
-  </si>
-  <si>
-    <t>Spec_Mage_Form1</t>
+    <t>头像Addressable完整路径(仅客户端)</t>
+  </si>
+  <si>
+    <t>魔法士</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Spec_Mage_Form2</t>
-  </si>
-  <si>
-    <t>Spec_Mage_Form3</t>
-  </si>
-  <si>
-    <t>Spec_Placeholder_02_Form1</t>
-  </si>
-  <si>
-    <t>Spec_Placeholder_02_Form2</t>
-  </si>
-  <si>
-    <t>Spec_Placeholder_02_Form3</t>
+    <t>魔法士(觉醒名待定)</t>
+  </si>
+  <si>
+    <t>魔法士(一次觉醒名待定)</t>
+  </si>
+  <si>
+    <t>占位专职</t>
+  </si>
+  <si>
+    <t>占位专职(觉醒)</t>
+  </si>
+  <si>
+    <t>占位专职(一次觉醒)</t>
   </si>
 </sst>
 </file>
@@ -494,7 +494,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8876D586-3654-4377-B791-7AD87A7FF5D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A14FC98-3933-4765-BB4A-C9DAB01408DF}">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
